--- a/datos_vaciados_camiones.xlsx
+++ b/datos_vaciados_camiones.xlsx
@@ -18802,6 +18802,5094 @@
         <v>0</v>
       </c>
     </row>
+    <row r="575">
+      <c r="A575" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B575" t="s">
+        <v>25</v>
+      </c>
+      <c r="C575" t="s">
+        <v>11</v>
+      </c>
+      <c r="D575" t="s">
+        <v>12</v>
+      </c>
+      <c r="E575" t="n">
+        <v>661</v>
+      </c>
+      <c r="F575" t="n">
+        <v>576</v>
+      </c>
+      <c r="G575" t="n">
+        <v>513</v>
+      </c>
+      <c r="H575" t="n">
+        <v>63</v>
+      </c>
+      <c r="I575" t="n">
+        <v>431</v>
+      </c>
+      <c r="J575" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B576" t="s">
+        <v>25</v>
+      </c>
+      <c r="C576" t="s">
+        <v>11</v>
+      </c>
+      <c r="D576" t="s">
+        <v>13</v>
+      </c>
+      <c r="E576" t="n">
+        <v>0</v>
+      </c>
+      <c r="F576" t="n">
+        <v>178</v>
+      </c>
+      <c r="G576" t="n">
+        <v>88</v>
+      </c>
+      <c r="H576" t="n">
+        <v>90</v>
+      </c>
+      <c r="I576" t="n">
+        <v>78</v>
+      </c>
+      <c r="J576" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B577" t="s">
+        <v>26</v>
+      </c>
+      <c r="C577" t="s">
+        <v>11</v>
+      </c>
+      <c r="D577" t="s">
+        <v>15</v>
+      </c>
+      <c r="E577" t="n">
+        <v>0</v>
+      </c>
+      <c r="F577" t="n">
+        <v>0</v>
+      </c>
+      <c r="G577" t="n">
+        <v>0</v>
+      </c>
+      <c r="H577" t="n">
+        <v>0</v>
+      </c>
+      <c r="I577" t="n">
+        <v>0</v>
+      </c>
+      <c r="J577" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B578" t="s">
+        <v>25</v>
+      </c>
+      <c r="C578" t="s">
+        <v>16</v>
+      </c>
+      <c r="D578" t="s">
+        <v>12</v>
+      </c>
+      <c r="E578" t="n">
+        <v>0</v>
+      </c>
+      <c r="F578" t="n">
+        <v>0</v>
+      </c>
+      <c r="G578" t="n">
+        <v>0</v>
+      </c>
+      <c r="H578" t="n">
+        <v>0</v>
+      </c>
+      <c r="I578" t="n">
+        <v>0</v>
+      </c>
+      <c r="J578" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B579" t="s">
+        <v>25</v>
+      </c>
+      <c r="C579" t="s">
+        <v>16</v>
+      </c>
+      <c r="D579" t="s">
+        <v>13</v>
+      </c>
+      <c r="E579" t="n">
+        <v>0</v>
+      </c>
+      <c r="F579" t="n">
+        <v>0</v>
+      </c>
+      <c r="G579" t="n">
+        <v>0</v>
+      </c>
+      <c r="H579" t="n">
+        <v>0</v>
+      </c>
+      <c r="I579" t="n">
+        <v>0</v>
+      </c>
+      <c r="J579" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B580" t="s">
+        <v>26</v>
+      </c>
+      <c r="C580" t="s">
+        <v>16</v>
+      </c>
+      <c r="D580" t="s">
+        <v>15</v>
+      </c>
+      <c r="E580" t="n">
+        <v>248</v>
+      </c>
+      <c r="F580" t="n">
+        <v>58</v>
+      </c>
+      <c r="G580" t="n">
+        <v>58</v>
+      </c>
+      <c r="H580" t="n">
+        <v>0</v>
+      </c>
+      <c r="I580" t="n">
+        <v>55</v>
+      </c>
+      <c r="J580" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B581" t="s">
+        <v>25</v>
+      </c>
+      <c r="C581" t="s">
+        <v>17</v>
+      </c>
+      <c r="D581" t="s">
+        <v>12</v>
+      </c>
+      <c r="E581" t="n">
+        <v>0</v>
+      </c>
+      <c r="F581" t="n">
+        <v>0</v>
+      </c>
+      <c r="G581" t="n">
+        <v>0</v>
+      </c>
+      <c r="H581" t="n">
+        <v>0</v>
+      </c>
+      <c r="I581" t="n">
+        <v>0</v>
+      </c>
+      <c r="J581" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B582" t="s">
+        <v>25</v>
+      </c>
+      <c r="C582" t="s">
+        <v>17</v>
+      </c>
+      <c r="D582" t="s">
+        <v>13</v>
+      </c>
+      <c r="E582" t="n">
+        <v>0</v>
+      </c>
+      <c r="F582" t="n">
+        <v>0</v>
+      </c>
+      <c r="G582" t="n">
+        <v>0</v>
+      </c>
+      <c r="H582" t="n">
+        <v>0</v>
+      </c>
+      <c r="I582" t="n">
+        <v>0</v>
+      </c>
+      <c r="J582" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B583" t="s">
+        <v>26</v>
+      </c>
+      <c r="C583" t="s">
+        <v>17</v>
+      </c>
+      <c r="D583" t="s">
+        <v>15</v>
+      </c>
+      <c r="E583" t="n">
+        <v>953</v>
+      </c>
+      <c r="F583" t="n">
+        <v>983</v>
+      </c>
+      <c r="G583" t="n">
+        <v>789</v>
+      </c>
+      <c r="H583" t="n">
+        <v>194</v>
+      </c>
+      <c r="I583" t="n">
+        <v>771</v>
+      </c>
+      <c r="J583" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B584" t="s">
+        <v>25</v>
+      </c>
+      <c r="C584" t="s">
+        <v>18</v>
+      </c>
+      <c r="D584" t="s">
+        <v>12</v>
+      </c>
+      <c r="E584" t="n">
+        <v>0</v>
+      </c>
+      <c r="F584" t="n">
+        <v>0</v>
+      </c>
+      <c r="G584" t="n">
+        <v>0</v>
+      </c>
+      <c r="H584" t="n">
+        <v>0</v>
+      </c>
+      <c r="I584" t="n">
+        <v>0</v>
+      </c>
+      <c r="J584" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B585" t="s">
+        <v>25</v>
+      </c>
+      <c r="C585" t="s">
+        <v>18</v>
+      </c>
+      <c r="D585" t="s">
+        <v>13</v>
+      </c>
+      <c r="E585" t="n">
+        <v>0</v>
+      </c>
+      <c r="F585" t="n">
+        <v>0</v>
+      </c>
+      <c r="G585" t="n">
+        <v>0</v>
+      </c>
+      <c r="H585" t="n">
+        <v>0</v>
+      </c>
+      <c r="I585" t="n">
+        <v>0</v>
+      </c>
+      <c r="J585" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B586" t="s">
+        <v>26</v>
+      </c>
+      <c r="C586" t="s">
+        <v>18</v>
+      </c>
+      <c r="D586" t="s">
+        <v>15</v>
+      </c>
+      <c r="E586" t="n">
+        <v>703</v>
+      </c>
+      <c r="F586" t="n">
+        <v>1067</v>
+      </c>
+      <c r="G586" t="n">
+        <v>1067</v>
+      </c>
+      <c r="H586" t="n">
+        <v>0</v>
+      </c>
+      <c r="I586" t="n">
+        <v>1058</v>
+      </c>
+      <c r="J586" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B587" t="s">
+        <v>25</v>
+      </c>
+      <c r="C587" t="s">
+        <v>19</v>
+      </c>
+      <c r="D587" t="s">
+        <v>12</v>
+      </c>
+      <c r="E587" t="n">
+        <v>667</v>
+      </c>
+      <c r="F587" t="n">
+        <v>512</v>
+      </c>
+      <c r="G587" t="n">
+        <v>318</v>
+      </c>
+      <c r="H587" t="n">
+        <v>194</v>
+      </c>
+      <c r="I587" t="n">
+        <v>269</v>
+      </c>
+      <c r="J587" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B588" t="s">
+        <v>25</v>
+      </c>
+      <c r="C588" t="s">
+        <v>19</v>
+      </c>
+      <c r="D588" t="s">
+        <v>13</v>
+      </c>
+      <c r="E588" t="n">
+        <v>260</v>
+      </c>
+      <c r="F588" t="n">
+        <v>310</v>
+      </c>
+      <c r="G588" t="n">
+        <v>137</v>
+      </c>
+      <c r="H588" t="n">
+        <v>173</v>
+      </c>
+      <c r="I588" t="n">
+        <v>116</v>
+      </c>
+      <c r="J588" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B589" t="s">
+        <v>26</v>
+      </c>
+      <c r="C589" t="s">
+        <v>19</v>
+      </c>
+      <c r="D589" t="s">
+        <v>15</v>
+      </c>
+      <c r="E589" t="n">
+        <v>0</v>
+      </c>
+      <c r="F589" t="n">
+        <v>0</v>
+      </c>
+      <c r="G589" t="n">
+        <v>0</v>
+      </c>
+      <c r="H589" t="n">
+        <v>0</v>
+      </c>
+      <c r="I589" t="n">
+        <v>0</v>
+      </c>
+      <c r="J589" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B590" t="s">
+        <v>25</v>
+      </c>
+      <c r="C590" t="s">
+        <v>20</v>
+      </c>
+      <c r="D590" t="s">
+        <v>12</v>
+      </c>
+      <c r="E590" t="n">
+        <v>57</v>
+      </c>
+      <c r="F590" t="n">
+        <v>201</v>
+      </c>
+      <c r="G590" t="n">
+        <v>110</v>
+      </c>
+      <c r="H590" t="n">
+        <v>91</v>
+      </c>
+      <c r="I590" t="n">
+        <v>101</v>
+      </c>
+      <c r="J590" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B591" t="s">
+        <v>25</v>
+      </c>
+      <c r="C591" t="s">
+        <v>20</v>
+      </c>
+      <c r="D591" t="s">
+        <v>13</v>
+      </c>
+      <c r="E591" t="n">
+        <v>233</v>
+      </c>
+      <c r="F591" t="n">
+        <v>132</v>
+      </c>
+      <c r="G591" t="n">
+        <v>84</v>
+      </c>
+      <c r="H591" t="n">
+        <v>48</v>
+      </c>
+      <c r="I591" t="n">
+        <v>78</v>
+      </c>
+      <c r="J591" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B592" t="s">
+        <v>26</v>
+      </c>
+      <c r="C592" t="s">
+        <v>20</v>
+      </c>
+      <c r="D592" t="s">
+        <v>15</v>
+      </c>
+      <c r="E592" t="n">
+        <v>220</v>
+      </c>
+      <c r="F592" t="n">
+        <v>283</v>
+      </c>
+      <c r="G592" t="n">
+        <v>243</v>
+      </c>
+      <c r="H592" t="n">
+        <v>40</v>
+      </c>
+      <c r="I592" t="n">
+        <v>236</v>
+      </c>
+      <c r="J592" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B593" t="s">
+        <v>25</v>
+      </c>
+      <c r="C593" t="s">
+        <v>21</v>
+      </c>
+      <c r="D593" t="s">
+        <v>12</v>
+      </c>
+      <c r="E593" t="n">
+        <v>285</v>
+      </c>
+      <c r="F593" t="n">
+        <v>721</v>
+      </c>
+      <c r="G593" t="n">
+        <v>398</v>
+      </c>
+      <c r="H593" t="n">
+        <v>323</v>
+      </c>
+      <c r="I593" t="n">
+        <v>360</v>
+      </c>
+      <c r="J593" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B594" t="s">
+        <v>25</v>
+      </c>
+      <c r="C594" t="s">
+        <v>21</v>
+      </c>
+      <c r="D594" t="s">
+        <v>13</v>
+      </c>
+      <c r="E594" t="n">
+        <v>0</v>
+      </c>
+      <c r="F594" t="n">
+        <v>100</v>
+      </c>
+      <c r="G594" t="n">
+        <v>55</v>
+      </c>
+      <c r="H594" t="n">
+        <v>45</v>
+      </c>
+      <c r="I594" t="n">
+        <v>49</v>
+      </c>
+      <c r="J594" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B595" t="s">
+        <v>26</v>
+      </c>
+      <c r="C595" t="s">
+        <v>21</v>
+      </c>
+      <c r="D595" t="s">
+        <v>15</v>
+      </c>
+      <c r="E595" t="n">
+        <v>0</v>
+      </c>
+      <c r="F595" t="n">
+        <v>0</v>
+      </c>
+      <c r="G595" t="n">
+        <v>0</v>
+      </c>
+      <c r="H595" t="n">
+        <v>0</v>
+      </c>
+      <c r="I595" t="n">
+        <v>0</v>
+      </c>
+      <c r="J595" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B596" t="s">
+        <v>25</v>
+      </c>
+      <c r="C596" t="s">
+        <v>22</v>
+      </c>
+      <c r="D596" t="s">
+        <v>12</v>
+      </c>
+      <c r="E596" t="n">
+        <v>0</v>
+      </c>
+      <c r="F596" t="n">
+        <v>318</v>
+      </c>
+      <c r="G596" t="n">
+        <v>191</v>
+      </c>
+      <c r="H596" t="n">
+        <v>127</v>
+      </c>
+      <c r="I596" t="n">
+        <v>168</v>
+      </c>
+      <c r="J596" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B597" t="s">
+        <v>25</v>
+      </c>
+      <c r="C597" t="s">
+        <v>22</v>
+      </c>
+      <c r="D597" t="s">
+        <v>13</v>
+      </c>
+      <c r="E597" t="n">
+        <v>728</v>
+      </c>
+      <c r="F597" t="n">
+        <v>162</v>
+      </c>
+      <c r="G597" t="n">
+        <v>115</v>
+      </c>
+      <c r="H597" t="n">
+        <v>47</v>
+      </c>
+      <c r="I597" t="n">
+        <v>107</v>
+      </c>
+      <c r="J597" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B598" t="s">
+        <v>26</v>
+      </c>
+      <c r="C598" t="s">
+        <v>22</v>
+      </c>
+      <c r="D598" t="s">
+        <v>15</v>
+      </c>
+      <c r="E598" t="n">
+        <v>0</v>
+      </c>
+      <c r="F598" t="n">
+        <v>0</v>
+      </c>
+      <c r="G598" t="n">
+        <v>0</v>
+      </c>
+      <c r="H598" t="n">
+        <v>0</v>
+      </c>
+      <c r="I598" t="n">
+        <v>0</v>
+      </c>
+      <c r="J598" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B599" t="s">
+        <v>26</v>
+      </c>
+      <c r="C599" t="s">
+        <v>11</v>
+      </c>
+      <c r="D599" t="s">
+        <v>12</v>
+      </c>
+      <c r="E599" t="n">
+        <v>621</v>
+      </c>
+      <c r="F599" t="n">
+        <v>107</v>
+      </c>
+      <c r="G599" t="n">
+        <v>86</v>
+      </c>
+      <c r="H599" t="n">
+        <v>21</v>
+      </c>
+      <c r="I599" t="n">
+        <v>85</v>
+      </c>
+      <c r="J599" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B600" t="s">
+        <v>26</v>
+      </c>
+      <c r="C600" t="s">
+        <v>11</v>
+      </c>
+      <c r="D600" t="s">
+        <v>13</v>
+      </c>
+      <c r="E600" t="n">
+        <v>0</v>
+      </c>
+      <c r="F600" t="n">
+        <v>0</v>
+      </c>
+      <c r="G600" t="n">
+        <v>0</v>
+      </c>
+      <c r="H600" t="n">
+        <v>0</v>
+      </c>
+      <c r="I600" t="n">
+        <v>0</v>
+      </c>
+      <c r="J600" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B601" t="s">
+        <v>27</v>
+      </c>
+      <c r="C601" t="s">
+        <v>11</v>
+      </c>
+      <c r="D601" t="s">
+        <v>15</v>
+      </c>
+      <c r="E601" t="n">
+        <v>0</v>
+      </c>
+      <c r="F601" t="n">
+        <v>0</v>
+      </c>
+      <c r="G601" t="n">
+        <v>0</v>
+      </c>
+      <c r="H601" t="n">
+        <v>0</v>
+      </c>
+      <c r="I601" t="n">
+        <v>0</v>
+      </c>
+      <c r="J601" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B602" t="s">
+        <v>26</v>
+      </c>
+      <c r="C602" t="s">
+        <v>16</v>
+      </c>
+      <c r="D602" t="s">
+        <v>12</v>
+      </c>
+      <c r="E602" t="n">
+        <v>0</v>
+      </c>
+      <c r="F602" t="n">
+        <v>0</v>
+      </c>
+      <c r="G602" t="n">
+        <v>0</v>
+      </c>
+      <c r="H602" t="n">
+        <v>0</v>
+      </c>
+      <c r="I602" t="n">
+        <v>0</v>
+      </c>
+      <c r="J602" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B603" t="s">
+        <v>26</v>
+      </c>
+      <c r="C603" t="s">
+        <v>16</v>
+      </c>
+      <c r="D603" t="s">
+        <v>13</v>
+      </c>
+      <c r="E603" t="n">
+        <v>0</v>
+      </c>
+      <c r="F603" t="n">
+        <v>0</v>
+      </c>
+      <c r="G603" t="n">
+        <v>0</v>
+      </c>
+      <c r="H603" t="n">
+        <v>0</v>
+      </c>
+      <c r="I603" t="n">
+        <v>0</v>
+      </c>
+      <c r="J603" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B604" t="s">
+        <v>27</v>
+      </c>
+      <c r="C604" t="s">
+        <v>16</v>
+      </c>
+      <c r="D604" t="s">
+        <v>15</v>
+      </c>
+      <c r="E604" t="n">
+        <v>45</v>
+      </c>
+      <c r="F604" t="n">
+        <v>252</v>
+      </c>
+      <c r="G604" t="n">
+        <v>252</v>
+      </c>
+      <c r="H604" t="n">
+        <v>0</v>
+      </c>
+      <c r="I604" t="n">
+        <v>244</v>
+      </c>
+      <c r="J604" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B605" t="s">
+        <v>26</v>
+      </c>
+      <c r="C605" t="s">
+        <v>17</v>
+      </c>
+      <c r="D605" t="s">
+        <v>12</v>
+      </c>
+      <c r="E605" t="n">
+        <v>0</v>
+      </c>
+      <c r="F605" t="n">
+        <v>0</v>
+      </c>
+      <c r="G605" t="n">
+        <v>0</v>
+      </c>
+      <c r="H605" t="n">
+        <v>0</v>
+      </c>
+      <c r="I605" t="n">
+        <v>0</v>
+      </c>
+      <c r="J605" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B606" t="s">
+        <v>26</v>
+      </c>
+      <c r="C606" t="s">
+        <v>17</v>
+      </c>
+      <c r="D606" t="s">
+        <v>13</v>
+      </c>
+      <c r="E606" t="n">
+        <v>0</v>
+      </c>
+      <c r="F606" t="n">
+        <v>0</v>
+      </c>
+      <c r="G606" t="n">
+        <v>0</v>
+      </c>
+      <c r="H606" t="n">
+        <v>0</v>
+      </c>
+      <c r="I606" t="n">
+        <v>0</v>
+      </c>
+      <c r="J606" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B607" t="s">
+        <v>27</v>
+      </c>
+      <c r="C607" t="s">
+        <v>17</v>
+      </c>
+      <c r="D607" t="s">
+        <v>15</v>
+      </c>
+      <c r="E607" t="n">
+        <v>694</v>
+      </c>
+      <c r="F607" t="n">
+        <v>566</v>
+      </c>
+      <c r="G607" t="n">
+        <v>558</v>
+      </c>
+      <c r="H607" t="n">
+        <v>8</v>
+      </c>
+      <c r="I607" t="n">
+        <v>548</v>
+      </c>
+      <c r="J607" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B608" t="s">
+        <v>26</v>
+      </c>
+      <c r="C608" t="s">
+        <v>18</v>
+      </c>
+      <c r="D608" t="s">
+        <v>12</v>
+      </c>
+      <c r="E608" t="n">
+        <v>0</v>
+      </c>
+      <c r="F608" t="n">
+        <v>0</v>
+      </c>
+      <c r="G608" t="n">
+        <v>0</v>
+      </c>
+      <c r="H608" t="n">
+        <v>0</v>
+      </c>
+      <c r="I608" t="n">
+        <v>0</v>
+      </c>
+      <c r="J608" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B609" t="s">
+        <v>26</v>
+      </c>
+      <c r="C609" t="s">
+        <v>18</v>
+      </c>
+      <c r="D609" t="s">
+        <v>13</v>
+      </c>
+      <c r="E609" t="n">
+        <v>0</v>
+      </c>
+      <c r="F609" t="n">
+        <v>0</v>
+      </c>
+      <c r="G609" t="n">
+        <v>0</v>
+      </c>
+      <c r="H609" t="n">
+        <v>0</v>
+      </c>
+      <c r="I609" t="n">
+        <v>0</v>
+      </c>
+      <c r="J609" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B610" t="s">
+        <v>27</v>
+      </c>
+      <c r="C610" t="s">
+        <v>18</v>
+      </c>
+      <c r="D610" t="s">
+        <v>15</v>
+      </c>
+      <c r="E610" t="n">
+        <v>953</v>
+      </c>
+      <c r="F610" t="n">
+        <v>716</v>
+      </c>
+      <c r="G610" t="n">
+        <v>630</v>
+      </c>
+      <c r="H610" t="n">
+        <v>86</v>
+      </c>
+      <c r="I610" t="n">
+        <v>620</v>
+      </c>
+      <c r="J610" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B611" t="s">
+        <v>26</v>
+      </c>
+      <c r="C611" t="s">
+        <v>19</v>
+      </c>
+      <c r="D611" t="s">
+        <v>12</v>
+      </c>
+      <c r="E611" t="n">
+        <v>346</v>
+      </c>
+      <c r="F611" t="n">
+        <v>339</v>
+      </c>
+      <c r="G611" t="n">
+        <v>263</v>
+      </c>
+      <c r="H611" t="n">
+        <v>76</v>
+      </c>
+      <c r="I611" t="n">
+        <v>238</v>
+      </c>
+      <c r="J611" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B612" t="s">
+        <v>26</v>
+      </c>
+      <c r="C612" t="s">
+        <v>19</v>
+      </c>
+      <c r="D612" t="s">
+        <v>13</v>
+      </c>
+      <c r="E612" t="n">
+        <v>0</v>
+      </c>
+      <c r="F612" t="n">
+        <v>0</v>
+      </c>
+      <c r="G612" t="n">
+        <v>0</v>
+      </c>
+      <c r="H612" t="n">
+        <v>0</v>
+      </c>
+      <c r="I612" t="n">
+        <v>0</v>
+      </c>
+      <c r="J612" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B613" t="s">
+        <v>27</v>
+      </c>
+      <c r="C613" t="s">
+        <v>19</v>
+      </c>
+      <c r="D613" t="s">
+        <v>15</v>
+      </c>
+      <c r="E613" t="n">
+        <v>98</v>
+      </c>
+      <c r="F613" t="n">
+        <v>99</v>
+      </c>
+      <c r="G613" t="n">
+        <v>99</v>
+      </c>
+      <c r="H613" t="n">
+        <v>0</v>
+      </c>
+      <c r="I613" t="n">
+        <v>92</v>
+      </c>
+      <c r="J613" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B614" t="s">
+        <v>26</v>
+      </c>
+      <c r="C614" t="s">
+        <v>20</v>
+      </c>
+      <c r="D614" t="s">
+        <v>12</v>
+      </c>
+      <c r="E614" t="n">
+        <v>0</v>
+      </c>
+      <c r="F614" t="n">
+        <v>1</v>
+      </c>
+      <c r="G614" t="n">
+        <v>1</v>
+      </c>
+      <c r="H614" t="n">
+        <v>0</v>
+      </c>
+      <c r="I614" t="n">
+        <v>1</v>
+      </c>
+      <c r="J614" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B615" t="s">
+        <v>26</v>
+      </c>
+      <c r="C615" t="s">
+        <v>20</v>
+      </c>
+      <c r="D615" t="s">
+        <v>13</v>
+      </c>
+      <c r="E615" t="n">
+        <v>0</v>
+      </c>
+      <c r="F615" t="n">
+        <v>0</v>
+      </c>
+      <c r="G615" t="n">
+        <v>0</v>
+      </c>
+      <c r="H615" t="n">
+        <v>0</v>
+      </c>
+      <c r="I615" t="n">
+        <v>0</v>
+      </c>
+      <c r="J615" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B616" t="s">
+        <v>27</v>
+      </c>
+      <c r="C616" t="s">
+        <v>20</v>
+      </c>
+      <c r="D616" t="s">
+        <v>15</v>
+      </c>
+      <c r="E616" t="n">
+        <v>796</v>
+      </c>
+      <c r="F616" t="n">
+        <v>453</v>
+      </c>
+      <c r="G616" t="n">
+        <v>360</v>
+      </c>
+      <c r="H616" t="n">
+        <v>93</v>
+      </c>
+      <c r="I616" t="n">
+        <v>355</v>
+      </c>
+      <c r="J616" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B617" t="s">
+        <v>26</v>
+      </c>
+      <c r="C617" t="s">
+        <v>21</v>
+      </c>
+      <c r="D617" t="s">
+        <v>12</v>
+      </c>
+      <c r="E617" t="n">
+        <v>718</v>
+      </c>
+      <c r="F617" t="n">
+        <v>716</v>
+      </c>
+      <c r="G617" t="n">
+        <v>519</v>
+      </c>
+      <c r="H617" t="n">
+        <v>197</v>
+      </c>
+      <c r="I617" t="n">
+        <v>448</v>
+      </c>
+      <c r="J617" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B618" t="s">
+        <v>26</v>
+      </c>
+      <c r="C618" t="s">
+        <v>21</v>
+      </c>
+      <c r="D618" t="s">
+        <v>13</v>
+      </c>
+      <c r="E618" t="n">
+        <v>0</v>
+      </c>
+      <c r="F618" t="n">
+        <v>0</v>
+      </c>
+      <c r="G618" t="n">
+        <v>0</v>
+      </c>
+      <c r="H618" t="n">
+        <v>0</v>
+      </c>
+      <c r="I618" t="n">
+        <v>0</v>
+      </c>
+      <c r="J618" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B619" t="s">
+        <v>27</v>
+      </c>
+      <c r="C619" t="s">
+        <v>21</v>
+      </c>
+      <c r="D619" t="s">
+        <v>15</v>
+      </c>
+      <c r="E619" t="n">
+        <v>0</v>
+      </c>
+      <c r="F619" t="n">
+        <v>0</v>
+      </c>
+      <c r="G619" t="n">
+        <v>0</v>
+      </c>
+      <c r="H619" t="n">
+        <v>0</v>
+      </c>
+      <c r="I619" t="n">
+        <v>0</v>
+      </c>
+      <c r="J619" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B620" t="s">
+        <v>26</v>
+      </c>
+      <c r="C620" t="s">
+        <v>22</v>
+      </c>
+      <c r="D620" t="s">
+        <v>12</v>
+      </c>
+      <c r="E620" t="n">
+        <v>0</v>
+      </c>
+      <c r="F620" t="n">
+        <v>118</v>
+      </c>
+      <c r="G620" t="n">
+        <v>88</v>
+      </c>
+      <c r="H620" t="n">
+        <v>30</v>
+      </c>
+      <c r="I620" t="n">
+        <v>76</v>
+      </c>
+      <c r="J620" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B621" t="s">
+        <v>26</v>
+      </c>
+      <c r="C621" t="s">
+        <v>22</v>
+      </c>
+      <c r="D621" t="s">
+        <v>13</v>
+      </c>
+      <c r="E621" t="n">
+        <v>0</v>
+      </c>
+      <c r="F621" t="n">
+        <v>0</v>
+      </c>
+      <c r="G621" t="n">
+        <v>0</v>
+      </c>
+      <c r="H621" t="n">
+        <v>0</v>
+      </c>
+      <c r="I621" t="n">
+        <v>0</v>
+      </c>
+      <c r="J621" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B622" t="s">
+        <v>27</v>
+      </c>
+      <c r="C622" t="s">
+        <v>22</v>
+      </c>
+      <c r="D622" t="s">
+        <v>15</v>
+      </c>
+      <c r="E622" t="n">
+        <v>0</v>
+      </c>
+      <c r="F622" t="n">
+        <v>168</v>
+      </c>
+      <c r="G622" t="n">
+        <v>107</v>
+      </c>
+      <c r="H622" t="n">
+        <v>61</v>
+      </c>
+      <c r="I622" t="n">
+        <v>103</v>
+      </c>
+      <c r="J622" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B623" t="s">
+        <v>27</v>
+      </c>
+      <c r="C623" t="s">
+        <v>11</v>
+      </c>
+      <c r="D623" t="s">
+        <v>12</v>
+      </c>
+      <c r="E623" t="n">
+        <v>661</v>
+      </c>
+      <c r="F623" t="n">
+        <v>515</v>
+      </c>
+      <c r="G623" t="n">
+        <v>277</v>
+      </c>
+      <c r="H623" t="n">
+        <v>238</v>
+      </c>
+      <c r="I623" t="n">
+        <v>249</v>
+      </c>
+      <c r="J623" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B624" t="s">
+        <v>27</v>
+      </c>
+      <c r="C624" t="s">
+        <v>11</v>
+      </c>
+      <c r="D624" t="s">
+        <v>13</v>
+      </c>
+      <c r="E624" t="n">
+        <v>0</v>
+      </c>
+      <c r="F624" t="n">
+        <v>234</v>
+      </c>
+      <c r="G624" t="n">
+        <v>103</v>
+      </c>
+      <c r="H624" t="n">
+        <v>131</v>
+      </c>
+      <c r="I624" t="n">
+        <v>97</v>
+      </c>
+      <c r="J624" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B625" t="s">
+        <v>10</v>
+      </c>
+      <c r="C625" t="s">
+        <v>11</v>
+      </c>
+      <c r="D625" t="s">
+        <v>15</v>
+      </c>
+      <c r="E625" t="n">
+        <v>0</v>
+      </c>
+      <c r="F625" t="n">
+        <v>0</v>
+      </c>
+      <c r="G625" t="n">
+        <v>0</v>
+      </c>
+      <c r="H625" t="n">
+        <v>0</v>
+      </c>
+      <c r="I625" t="n">
+        <v>0</v>
+      </c>
+      <c r="J625" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B626" t="s">
+        <v>27</v>
+      </c>
+      <c r="C626" t="s">
+        <v>16</v>
+      </c>
+      <c r="D626" t="s">
+        <v>12</v>
+      </c>
+      <c r="E626" t="n">
+        <v>0</v>
+      </c>
+      <c r="F626" t="n">
+        <v>0</v>
+      </c>
+      <c r="G626" t="n">
+        <v>0</v>
+      </c>
+      <c r="H626" t="n">
+        <v>0</v>
+      </c>
+      <c r="I626" t="n">
+        <v>0</v>
+      </c>
+      <c r="J626" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B627" t="s">
+        <v>27</v>
+      </c>
+      <c r="C627" t="s">
+        <v>16</v>
+      </c>
+      <c r="D627" t="s">
+        <v>13</v>
+      </c>
+      <c r="E627" t="n">
+        <v>0</v>
+      </c>
+      <c r="F627" t="n">
+        <v>0</v>
+      </c>
+      <c r="G627" t="n">
+        <v>0</v>
+      </c>
+      <c r="H627" t="n">
+        <v>0</v>
+      </c>
+      <c r="I627" t="n">
+        <v>0</v>
+      </c>
+      <c r="J627" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B628" t="s">
+        <v>10</v>
+      </c>
+      <c r="C628" t="s">
+        <v>16</v>
+      </c>
+      <c r="D628" t="s">
+        <v>15</v>
+      </c>
+      <c r="E628" t="n">
+        <v>248</v>
+      </c>
+      <c r="F628" t="n">
+        <v>48</v>
+      </c>
+      <c r="G628" t="n">
+        <v>48</v>
+      </c>
+      <c r="H628" t="n">
+        <v>0</v>
+      </c>
+      <c r="I628" t="n">
+        <v>45</v>
+      </c>
+      <c r="J628" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B629" t="s">
+        <v>27</v>
+      </c>
+      <c r="C629" t="s">
+        <v>17</v>
+      </c>
+      <c r="D629" t="s">
+        <v>12</v>
+      </c>
+      <c r="E629" t="n">
+        <v>0</v>
+      </c>
+      <c r="F629" t="n">
+        <v>0</v>
+      </c>
+      <c r="G629" t="n">
+        <v>0</v>
+      </c>
+      <c r="H629" t="n">
+        <v>0</v>
+      </c>
+      <c r="I629" t="n">
+        <v>0</v>
+      </c>
+      <c r="J629" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B630" t="s">
+        <v>27</v>
+      </c>
+      <c r="C630" t="s">
+        <v>17</v>
+      </c>
+      <c r="D630" t="s">
+        <v>13</v>
+      </c>
+      <c r="E630" t="n">
+        <v>0</v>
+      </c>
+      <c r="F630" t="n">
+        <v>0</v>
+      </c>
+      <c r="G630" t="n">
+        <v>0</v>
+      </c>
+      <c r="H630" t="n">
+        <v>0</v>
+      </c>
+      <c r="I630" t="n">
+        <v>0</v>
+      </c>
+      <c r="J630" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B631" t="s">
+        <v>10</v>
+      </c>
+      <c r="C631" t="s">
+        <v>17</v>
+      </c>
+      <c r="D631" t="s">
+        <v>15</v>
+      </c>
+      <c r="E631" t="n">
+        <v>949</v>
+      </c>
+      <c r="F631" t="n">
+        <v>761</v>
+      </c>
+      <c r="G631" t="n">
+        <v>690</v>
+      </c>
+      <c r="H631" t="n">
+        <v>71</v>
+      </c>
+      <c r="I631" t="n">
+        <v>675</v>
+      </c>
+      <c r="J631" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B632" t="s">
+        <v>27</v>
+      </c>
+      <c r="C632" t="s">
+        <v>18</v>
+      </c>
+      <c r="D632" t="s">
+        <v>12</v>
+      </c>
+      <c r="E632" t="n">
+        <v>0</v>
+      </c>
+      <c r="F632" t="n">
+        <v>0</v>
+      </c>
+      <c r="G632" t="n">
+        <v>0</v>
+      </c>
+      <c r="H632" t="n">
+        <v>0</v>
+      </c>
+      <c r="I632" t="n">
+        <v>0</v>
+      </c>
+      <c r="J632" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B633" t="s">
+        <v>27</v>
+      </c>
+      <c r="C633" t="s">
+        <v>18</v>
+      </c>
+      <c r="D633" t="s">
+        <v>13</v>
+      </c>
+      <c r="E633" t="n">
+        <v>0</v>
+      </c>
+      <c r="F633" t="n">
+        <v>0</v>
+      </c>
+      <c r="G633" t="n">
+        <v>0</v>
+      </c>
+      <c r="H633" t="n">
+        <v>0</v>
+      </c>
+      <c r="I633" t="n">
+        <v>0</v>
+      </c>
+      <c r="J633" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B634" t="s">
+        <v>10</v>
+      </c>
+      <c r="C634" t="s">
+        <v>18</v>
+      </c>
+      <c r="D634" t="s">
+        <v>15</v>
+      </c>
+      <c r="E634" t="n">
+        <v>704</v>
+      </c>
+      <c r="F634" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G634" t="n">
+        <v>1002</v>
+      </c>
+      <c r="H634" t="n">
+        <v>118</v>
+      </c>
+      <c r="I634" t="n">
+        <v>992</v>
+      </c>
+      <c r="J634" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B635" t="s">
+        <v>27</v>
+      </c>
+      <c r="C635" t="s">
+        <v>19</v>
+      </c>
+      <c r="D635" t="s">
+        <v>12</v>
+      </c>
+      <c r="E635" t="n">
+        <v>670</v>
+      </c>
+      <c r="F635" t="n">
+        <v>655</v>
+      </c>
+      <c r="G635" t="n">
+        <v>321</v>
+      </c>
+      <c r="H635" t="n">
+        <v>334</v>
+      </c>
+      <c r="I635" t="n">
+        <v>277</v>
+      </c>
+      <c r="J635" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B636" t="s">
+        <v>27</v>
+      </c>
+      <c r="C636" t="s">
+        <v>19</v>
+      </c>
+      <c r="D636" t="s">
+        <v>13</v>
+      </c>
+      <c r="E636" t="n">
+        <v>260</v>
+      </c>
+      <c r="F636" t="n">
+        <v>105</v>
+      </c>
+      <c r="G636" t="n">
+        <v>57</v>
+      </c>
+      <c r="H636" t="n">
+        <v>48</v>
+      </c>
+      <c r="I636" t="n">
+        <v>52</v>
+      </c>
+      <c r="J636" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B637" t="s">
+        <v>10</v>
+      </c>
+      <c r="C637" t="s">
+        <v>19</v>
+      </c>
+      <c r="D637" t="s">
+        <v>15</v>
+      </c>
+      <c r="E637" t="n">
+        <v>0</v>
+      </c>
+      <c r="F637" t="n">
+        <v>0</v>
+      </c>
+      <c r="G637" t="n">
+        <v>0</v>
+      </c>
+      <c r="H637" t="n">
+        <v>0</v>
+      </c>
+      <c r="I637" t="n">
+        <v>0</v>
+      </c>
+      <c r="J637" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B638" t="s">
+        <v>27</v>
+      </c>
+      <c r="C638" t="s">
+        <v>20</v>
+      </c>
+      <c r="D638" t="s">
+        <v>12</v>
+      </c>
+      <c r="E638" t="n">
+        <v>57</v>
+      </c>
+      <c r="F638" t="n">
+        <v>303</v>
+      </c>
+      <c r="G638" t="n">
+        <v>203</v>
+      </c>
+      <c r="H638" t="n">
+        <v>100</v>
+      </c>
+      <c r="I638" t="n">
+        <v>178</v>
+      </c>
+      <c r="J638" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B639" t="s">
+        <v>27</v>
+      </c>
+      <c r="C639" t="s">
+        <v>20</v>
+      </c>
+      <c r="D639" t="s">
+        <v>13</v>
+      </c>
+      <c r="E639" t="n">
+        <v>233</v>
+      </c>
+      <c r="F639" t="n">
+        <v>145</v>
+      </c>
+      <c r="G639" t="n">
+        <v>145</v>
+      </c>
+      <c r="H639" t="n">
+        <v>0</v>
+      </c>
+      <c r="I639" t="n">
+        <v>128</v>
+      </c>
+      <c r="J639" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B640" t="s">
+        <v>10</v>
+      </c>
+      <c r="C640" t="s">
+        <v>20</v>
+      </c>
+      <c r="D640" t="s">
+        <v>15</v>
+      </c>
+      <c r="E640" t="n">
+        <v>187</v>
+      </c>
+      <c r="F640" t="n">
+        <v>554</v>
+      </c>
+      <c r="G640" t="n">
+        <v>354</v>
+      </c>
+      <c r="H640" t="n">
+        <v>200</v>
+      </c>
+      <c r="I640" t="n">
+        <v>344</v>
+      </c>
+      <c r="J640" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B641" t="s">
+        <v>27</v>
+      </c>
+      <c r="C641" t="s">
+        <v>21</v>
+      </c>
+      <c r="D641" t="s">
+        <v>12</v>
+      </c>
+      <c r="E641" t="n">
+        <v>285</v>
+      </c>
+      <c r="F641" t="n">
+        <v>505</v>
+      </c>
+      <c r="G641" t="n">
+        <v>276</v>
+      </c>
+      <c r="H641" t="n">
+        <v>229</v>
+      </c>
+      <c r="I641" t="n">
+        <v>248</v>
+      </c>
+      <c r="J641" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B642" t="s">
+        <v>27</v>
+      </c>
+      <c r="C642" t="s">
+        <v>21</v>
+      </c>
+      <c r="D642" t="s">
+        <v>13</v>
+      </c>
+      <c r="E642" t="n">
+        <v>0</v>
+      </c>
+      <c r="F642" t="n">
+        <v>301</v>
+      </c>
+      <c r="G642" t="n">
+        <v>138</v>
+      </c>
+      <c r="H642" t="n">
+        <v>163</v>
+      </c>
+      <c r="I642" t="n">
+        <v>114</v>
+      </c>
+      <c r="J642" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B643" t="s">
+        <v>10</v>
+      </c>
+      <c r="C643" t="s">
+        <v>21</v>
+      </c>
+      <c r="D643" t="s">
+        <v>15</v>
+      </c>
+      <c r="E643" t="n">
+        <v>0</v>
+      </c>
+      <c r="F643" t="n">
+        <v>0</v>
+      </c>
+      <c r="G643" t="n">
+        <v>0</v>
+      </c>
+      <c r="H643" t="n">
+        <v>0</v>
+      </c>
+      <c r="I643" t="n">
+        <v>0</v>
+      </c>
+      <c r="J643" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B644" t="s">
+        <v>27</v>
+      </c>
+      <c r="C644" t="s">
+        <v>22</v>
+      </c>
+      <c r="D644" t="s">
+        <v>12</v>
+      </c>
+      <c r="E644" t="n">
+        <v>0</v>
+      </c>
+      <c r="F644" t="n">
+        <v>712</v>
+      </c>
+      <c r="G644" t="n">
+        <v>415</v>
+      </c>
+      <c r="H644" t="n">
+        <v>297</v>
+      </c>
+      <c r="I644" t="n">
+        <v>367</v>
+      </c>
+      <c r="J644" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B645" t="s">
+        <v>27</v>
+      </c>
+      <c r="C645" t="s">
+        <v>22</v>
+      </c>
+      <c r="D645" t="s">
+        <v>13</v>
+      </c>
+      <c r="E645" t="n">
+        <v>728</v>
+      </c>
+      <c r="F645" t="n">
+        <v>497</v>
+      </c>
+      <c r="G645" t="n">
+        <v>305</v>
+      </c>
+      <c r="H645" t="n">
+        <v>192</v>
+      </c>
+      <c r="I645" t="n">
+        <v>267</v>
+      </c>
+      <c r="J645" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B646" t="s">
+        <v>10</v>
+      </c>
+      <c r="C646" t="s">
+        <v>22</v>
+      </c>
+      <c r="D646" t="s">
+        <v>15</v>
+      </c>
+      <c r="E646" t="n">
+        <v>0</v>
+      </c>
+      <c r="F646" t="n">
+        <v>0</v>
+      </c>
+      <c r="G646" t="n">
+        <v>0</v>
+      </c>
+      <c r="H646" t="n">
+        <v>0</v>
+      </c>
+      <c r="I646" t="n">
+        <v>0</v>
+      </c>
+      <c r="J646" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B647" t="s">
+        <v>10</v>
+      </c>
+      <c r="C647" t="s">
+        <v>11</v>
+      </c>
+      <c r="D647" t="s">
+        <v>12</v>
+      </c>
+      <c r="E647" t="n">
+        <v>621</v>
+      </c>
+      <c r="F647" t="n">
+        <v>1003</v>
+      </c>
+      <c r="G647" t="n">
+        <v>515</v>
+      </c>
+      <c r="H647" t="n">
+        <v>488</v>
+      </c>
+      <c r="I647" t="n">
+        <v>465</v>
+      </c>
+      <c r="J647" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B648" t="s">
+        <v>10</v>
+      </c>
+      <c r="C648" t="s">
+        <v>11</v>
+      </c>
+      <c r="D648" t="s">
+        <v>13</v>
+      </c>
+      <c r="E648" t="n">
+        <v>0</v>
+      </c>
+      <c r="F648" t="n">
+        <v>295</v>
+      </c>
+      <c r="G648" t="n">
+        <v>159</v>
+      </c>
+      <c r="H648" t="n">
+        <v>136</v>
+      </c>
+      <c r="I648" t="n">
+        <v>148</v>
+      </c>
+      <c r="J648" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B649" t="s">
+        <v>14</v>
+      </c>
+      <c r="C649" t="s">
+        <v>11</v>
+      </c>
+      <c r="D649" t="s">
+        <v>15</v>
+      </c>
+      <c r="E649" t="n">
+        <v>0</v>
+      </c>
+      <c r="F649" t="n">
+        <v>0</v>
+      </c>
+      <c r="G649" t="n">
+        <v>0</v>
+      </c>
+      <c r="H649" t="n">
+        <v>0</v>
+      </c>
+      <c r="I649" t="n">
+        <v>0</v>
+      </c>
+      <c r="J649" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B650" t="s">
+        <v>10</v>
+      </c>
+      <c r="C650" t="s">
+        <v>16</v>
+      </c>
+      <c r="D650" t="s">
+        <v>12</v>
+      </c>
+      <c r="E650" t="n">
+        <v>0</v>
+      </c>
+      <c r="F650" t="n">
+        <v>0</v>
+      </c>
+      <c r="G650" t="n">
+        <v>0</v>
+      </c>
+      <c r="H650" t="n">
+        <v>0</v>
+      </c>
+      <c r="I650" t="n">
+        <v>0</v>
+      </c>
+      <c r="J650" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B651" t="s">
+        <v>10</v>
+      </c>
+      <c r="C651" t="s">
+        <v>16</v>
+      </c>
+      <c r="D651" t="s">
+        <v>13</v>
+      </c>
+      <c r="E651" t="n">
+        <v>0</v>
+      </c>
+      <c r="F651" t="n">
+        <v>0</v>
+      </c>
+      <c r="G651" t="n">
+        <v>0</v>
+      </c>
+      <c r="H651" t="n">
+        <v>0</v>
+      </c>
+      <c r="I651" t="n">
+        <v>0</v>
+      </c>
+      <c r="J651" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B652" t="s">
+        <v>14</v>
+      </c>
+      <c r="C652" t="s">
+        <v>16</v>
+      </c>
+      <c r="D652" t="s">
+        <v>15</v>
+      </c>
+      <c r="E652" t="n">
+        <v>45</v>
+      </c>
+      <c r="F652" t="n">
+        <v>52</v>
+      </c>
+      <c r="G652" t="n">
+        <v>51</v>
+      </c>
+      <c r="H652" t="n">
+        <v>1</v>
+      </c>
+      <c r="I652" t="n">
+        <v>48</v>
+      </c>
+      <c r="J652" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B653" t="s">
+        <v>10</v>
+      </c>
+      <c r="C653" t="s">
+        <v>17</v>
+      </c>
+      <c r="D653" t="s">
+        <v>12</v>
+      </c>
+      <c r="E653" t="n">
+        <v>0</v>
+      </c>
+      <c r="F653" t="n">
+        <v>0</v>
+      </c>
+      <c r="G653" t="n">
+        <v>0</v>
+      </c>
+      <c r="H653" t="n">
+        <v>0</v>
+      </c>
+      <c r="I653" t="n">
+        <v>0</v>
+      </c>
+      <c r="J653" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B654" t="s">
+        <v>10</v>
+      </c>
+      <c r="C654" t="s">
+        <v>17</v>
+      </c>
+      <c r="D654" t="s">
+        <v>13</v>
+      </c>
+      <c r="E654" t="n">
+        <v>0</v>
+      </c>
+      <c r="F654" t="n">
+        <v>0</v>
+      </c>
+      <c r="G654" t="n">
+        <v>0</v>
+      </c>
+      <c r="H654" t="n">
+        <v>0</v>
+      </c>
+      <c r="I654" t="n">
+        <v>0</v>
+      </c>
+      <c r="J654" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B655" t="s">
+        <v>14</v>
+      </c>
+      <c r="C655" t="s">
+        <v>17</v>
+      </c>
+      <c r="D655" t="s">
+        <v>15</v>
+      </c>
+      <c r="E655" t="n">
+        <v>694</v>
+      </c>
+      <c r="F655" t="n">
+        <v>696</v>
+      </c>
+      <c r="G655" t="n">
+        <v>555</v>
+      </c>
+      <c r="H655" t="n">
+        <v>141</v>
+      </c>
+      <c r="I655" t="n">
+        <v>547</v>
+      </c>
+      <c r="J655" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B656" t="s">
+        <v>10</v>
+      </c>
+      <c r="C656" t="s">
+        <v>18</v>
+      </c>
+      <c r="D656" t="s">
+        <v>12</v>
+      </c>
+      <c r="E656" t="n">
+        <v>0</v>
+      </c>
+      <c r="F656" t="n">
+        <v>0</v>
+      </c>
+      <c r="G656" t="n">
+        <v>0</v>
+      </c>
+      <c r="H656" t="n">
+        <v>0</v>
+      </c>
+      <c r="I656" t="n">
+        <v>0</v>
+      </c>
+      <c r="J656" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B657" t="s">
+        <v>10</v>
+      </c>
+      <c r="C657" t="s">
+        <v>18</v>
+      </c>
+      <c r="D657" t="s">
+        <v>13</v>
+      </c>
+      <c r="E657" t="n">
+        <v>0</v>
+      </c>
+      <c r="F657" t="n">
+        <v>0</v>
+      </c>
+      <c r="G657" t="n">
+        <v>0</v>
+      </c>
+      <c r="H657" t="n">
+        <v>0</v>
+      </c>
+      <c r="I657" t="n">
+        <v>0</v>
+      </c>
+      <c r="J657" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B658" t="s">
+        <v>14</v>
+      </c>
+      <c r="C658" t="s">
+        <v>18</v>
+      </c>
+      <c r="D658" t="s">
+        <v>15</v>
+      </c>
+      <c r="E658" t="n">
+        <v>953</v>
+      </c>
+      <c r="F658" t="n">
+        <v>788</v>
+      </c>
+      <c r="G658" t="n">
+        <v>784</v>
+      </c>
+      <c r="H658" t="n">
+        <v>4</v>
+      </c>
+      <c r="I658" t="n">
+        <v>769</v>
+      </c>
+      <c r="J658" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B659" t="s">
+        <v>10</v>
+      </c>
+      <c r="C659" t="s">
+        <v>19</v>
+      </c>
+      <c r="D659" t="s">
+        <v>12</v>
+      </c>
+      <c r="E659" t="n">
+        <v>346</v>
+      </c>
+      <c r="F659" t="n">
+        <v>626</v>
+      </c>
+      <c r="G659" t="n">
+        <v>394</v>
+      </c>
+      <c r="H659" t="n">
+        <v>232</v>
+      </c>
+      <c r="I659" t="n">
+        <v>329</v>
+      </c>
+      <c r="J659" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B660" t="s">
+        <v>10</v>
+      </c>
+      <c r="C660" t="s">
+        <v>19</v>
+      </c>
+      <c r="D660" t="s">
+        <v>13</v>
+      </c>
+      <c r="E660" t="n">
+        <v>0</v>
+      </c>
+      <c r="F660" t="n">
+        <v>124</v>
+      </c>
+      <c r="G660" t="n">
+        <v>56</v>
+      </c>
+      <c r="H660" t="n">
+        <v>68</v>
+      </c>
+      <c r="I660" t="n">
+        <v>42</v>
+      </c>
+      <c r="J660" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B661" t="s">
+        <v>14</v>
+      </c>
+      <c r="C661" t="s">
+        <v>19</v>
+      </c>
+      <c r="D661" t="s">
+        <v>15</v>
+      </c>
+      <c r="E661" t="n">
+        <v>97</v>
+      </c>
+      <c r="F661" t="n">
+        <v>100</v>
+      </c>
+      <c r="G661" t="n">
+        <v>99</v>
+      </c>
+      <c r="H661" t="n">
+        <v>1</v>
+      </c>
+      <c r="I661" t="n">
+        <v>93</v>
+      </c>
+      <c r="J661" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B662" t="s">
+        <v>10</v>
+      </c>
+      <c r="C662" t="s">
+        <v>20</v>
+      </c>
+      <c r="D662" t="s">
+        <v>12</v>
+      </c>
+      <c r="E662" t="n">
+        <v>0</v>
+      </c>
+      <c r="F662" t="n">
+        <v>0</v>
+      </c>
+      <c r="G662" t="n">
+        <v>0</v>
+      </c>
+      <c r="H662" t="n">
+        <v>0</v>
+      </c>
+      <c r="I662" t="n">
+        <v>0</v>
+      </c>
+      <c r="J662" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B663" t="s">
+        <v>10</v>
+      </c>
+      <c r="C663" t="s">
+        <v>20</v>
+      </c>
+      <c r="D663" t="s">
+        <v>13</v>
+      </c>
+      <c r="E663" t="n">
+        <v>99</v>
+      </c>
+      <c r="F663" t="n">
+        <v>42</v>
+      </c>
+      <c r="G663" t="n">
+        <v>42</v>
+      </c>
+      <c r="H663" t="n">
+        <v>0</v>
+      </c>
+      <c r="I663" t="n">
+        <v>41</v>
+      </c>
+      <c r="J663" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B664" t="s">
+        <v>14</v>
+      </c>
+      <c r="C664" t="s">
+        <v>20</v>
+      </c>
+      <c r="D664" t="s">
+        <v>15</v>
+      </c>
+      <c r="E664" t="n">
+        <v>828</v>
+      </c>
+      <c r="F664" t="n">
+        <v>508</v>
+      </c>
+      <c r="G664" t="n">
+        <v>473</v>
+      </c>
+      <c r="H664" t="n">
+        <v>35</v>
+      </c>
+      <c r="I664" t="n">
+        <v>467</v>
+      </c>
+      <c r="J664" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B665" t="s">
+        <v>10</v>
+      </c>
+      <c r="C665" t="s">
+        <v>21</v>
+      </c>
+      <c r="D665" t="s">
+        <v>12</v>
+      </c>
+      <c r="E665" t="n">
+        <v>717</v>
+      </c>
+      <c r="F665" t="n">
+        <v>364</v>
+      </c>
+      <c r="G665" t="n">
+        <v>210</v>
+      </c>
+      <c r="H665" t="n">
+        <v>154</v>
+      </c>
+      <c r="I665" t="n">
+        <v>182</v>
+      </c>
+      <c r="J665" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B666" t="s">
+        <v>10</v>
+      </c>
+      <c r="C666" t="s">
+        <v>21</v>
+      </c>
+      <c r="D666" t="s">
+        <v>13</v>
+      </c>
+      <c r="E666" t="n">
+        <v>387</v>
+      </c>
+      <c r="F666" t="n">
+        <v>181</v>
+      </c>
+      <c r="G666" t="n">
+        <v>129</v>
+      </c>
+      <c r="H666" t="n">
+        <v>52</v>
+      </c>
+      <c r="I666" t="n">
+        <v>114</v>
+      </c>
+      <c r="J666" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B667" t="s">
+        <v>14</v>
+      </c>
+      <c r="C667" t="s">
+        <v>21</v>
+      </c>
+      <c r="D667" t="s">
+        <v>15</v>
+      </c>
+      <c r="E667" t="n">
+        <v>0</v>
+      </c>
+      <c r="F667" t="n">
+        <v>0</v>
+      </c>
+      <c r="G667" t="n">
+        <v>0</v>
+      </c>
+      <c r="H667" t="n">
+        <v>0</v>
+      </c>
+      <c r="I667" t="n">
+        <v>0</v>
+      </c>
+      <c r="J667" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B668" t="s">
+        <v>10</v>
+      </c>
+      <c r="C668" t="s">
+        <v>22</v>
+      </c>
+      <c r="D668" t="s">
+        <v>12</v>
+      </c>
+      <c r="E668" t="n">
+        <v>0</v>
+      </c>
+      <c r="F668" t="n">
+        <v>366</v>
+      </c>
+      <c r="G668" t="n">
+        <v>144</v>
+      </c>
+      <c r="H668" t="n">
+        <v>222</v>
+      </c>
+      <c r="I668" t="n">
+        <v>116</v>
+      </c>
+      <c r="J668" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B669" t="s">
+        <v>10</v>
+      </c>
+      <c r="C669" t="s">
+        <v>22</v>
+      </c>
+      <c r="D669" t="s">
+        <v>13</v>
+      </c>
+      <c r="E669" t="n">
+        <v>641</v>
+      </c>
+      <c r="F669" t="n">
+        <v>298</v>
+      </c>
+      <c r="G669" t="n">
+        <v>208</v>
+      </c>
+      <c r="H669" t="n">
+        <v>90</v>
+      </c>
+      <c r="I669" t="n">
+        <v>196</v>
+      </c>
+      <c r="J669" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B670" t="s">
+        <v>14</v>
+      </c>
+      <c r="C670" t="s">
+        <v>22</v>
+      </c>
+      <c r="D670" t="s">
+        <v>15</v>
+      </c>
+      <c r="E670" t="n">
+        <v>0</v>
+      </c>
+      <c r="F670" t="n">
+        <v>0</v>
+      </c>
+      <c r="G670" t="n">
+        <v>0</v>
+      </c>
+      <c r="H670" t="n">
+        <v>0</v>
+      </c>
+      <c r="I670" t="n">
+        <v>0</v>
+      </c>
+      <c r="J670" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B671" t="s">
+        <v>14</v>
+      </c>
+      <c r="C671" t="s">
+        <v>11</v>
+      </c>
+      <c r="D671" t="s">
+        <v>12</v>
+      </c>
+      <c r="E671" t="n">
+        <v>659</v>
+      </c>
+      <c r="F671" t="n">
+        <v>438</v>
+      </c>
+      <c r="G671" t="n">
+        <v>231</v>
+      </c>
+      <c r="H671" t="n">
+        <v>207</v>
+      </c>
+      <c r="I671" t="n">
+        <v>202</v>
+      </c>
+      <c r="J671" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B672" t="s">
+        <v>14</v>
+      </c>
+      <c r="C672" t="s">
+        <v>11</v>
+      </c>
+      <c r="D672" t="s">
+        <v>13</v>
+      </c>
+      <c r="E672" t="n">
+        <v>0</v>
+      </c>
+      <c r="F672" t="n">
+        <v>69</v>
+      </c>
+      <c r="G672" t="n">
+        <v>31</v>
+      </c>
+      <c r="H672" t="n">
+        <v>38</v>
+      </c>
+      <c r="I672" t="n">
+        <v>30</v>
+      </c>
+      <c r="J672" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B673" t="s">
+        <v>23</v>
+      </c>
+      <c r="C673" t="s">
+        <v>11</v>
+      </c>
+      <c r="D673" t="s">
+        <v>15</v>
+      </c>
+      <c r="E673" t="n">
+        <v>0</v>
+      </c>
+      <c r="F673" t="n">
+        <v>0</v>
+      </c>
+      <c r="G673" t="n">
+        <v>0</v>
+      </c>
+      <c r="H673" t="n">
+        <v>0</v>
+      </c>
+      <c r="I673" t="n">
+        <v>0</v>
+      </c>
+      <c r="J673" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B674" t="s">
+        <v>14</v>
+      </c>
+      <c r="C674" t="s">
+        <v>19</v>
+      </c>
+      <c r="D674" t="s">
+        <v>12</v>
+      </c>
+      <c r="E674" t="n">
+        <v>669</v>
+      </c>
+      <c r="F674" t="n">
+        <v>621</v>
+      </c>
+      <c r="G674" t="n">
+        <v>510</v>
+      </c>
+      <c r="H674" t="n">
+        <v>111</v>
+      </c>
+      <c r="I674" t="n">
+        <v>427</v>
+      </c>
+      <c r="J674" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B675" t="s">
+        <v>14</v>
+      </c>
+      <c r="C675" t="s">
+        <v>19</v>
+      </c>
+      <c r="D675" t="s">
+        <v>13</v>
+      </c>
+      <c r="E675" t="n">
+        <v>261</v>
+      </c>
+      <c r="F675" t="n">
+        <v>84</v>
+      </c>
+      <c r="G675" t="n">
+        <v>62</v>
+      </c>
+      <c r="H675" t="n">
+        <v>22</v>
+      </c>
+      <c r="I675" t="n">
+        <v>52</v>
+      </c>
+      <c r="J675" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B676" t="s">
+        <v>23</v>
+      </c>
+      <c r="C676" t="s">
+        <v>19</v>
+      </c>
+      <c r="D676" t="s">
+        <v>15</v>
+      </c>
+      <c r="E676" t="n">
+        <v>0</v>
+      </c>
+      <c r="F676" t="n">
+        <v>0</v>
+      </c>
+      <c r="G676" t="n">
+        <v>0</v>
+      </c>
+      <c r="H676" t="n">
+        <v>0</v>
+      </c>
+      <c r="I676" t="n">
+        <v>0</v>
+      </c>
+      <c r="J676" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B677" t="s">
+        <v>14</v>
+      </c>
+      <c r="C677" t="s">
+        <v>20</v>
+      </c>
+      <c r="D677" t="s">
+        <v>12</v>
+      </c>
+      <c r="E677" t="n">
+        <v>57</v>
+      </c>
+      <c r="F677" t="n">
+        <v>111</v>
+      </c>
+      <c r="G677" t="n">
+        <v>0</v>
+      </c>
+      <c r="H677" t="n">
+        <v>111</v>
+      </c>
+      <c r="I677" t="n">
+        <v>0</v>
+      </c>
+      <c r="J677" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B678" t="s">
+        <v>14</v>
+      </c>
+      <c r="C678" t="s">
+        <v>20</v>
+      </c>
+      <c r="D678" t="s">
+        <v>13</v>
+      </c>
+      <c r="E678" t="n">
+        <v>232</v>
+      </c>
+      <c r="F678" t="n">
+        <v>209</v>
+      </c>
+      <c r="G678" t="n">
+        <v>119</v>
+      </c>
+      <c r="H678" t="n">
+        <v>90</v>
+      </c>
+      <c r="I678" t="n">
+        <v>112</v>
+      </c>
+      <c r="J678" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B679" t="s">
+        <v>23</v>
+      </c>
+      <c r="C679" t="s">
+        <v>20</v>
+      </c>
+      <c r="D679" t="s">
+        <v>15</v>
+      </c>
+      <c r="E679" t="n">
+        <v>0</v>
+      </c>
+      <c r="F679" t="n">
+        <v>0</v>
+      </c>
+      <c r="G679" t="n">
+        <v>0</v>
+      </c>
+      <c r="H679" t="n">
+        <v>0</v>
+      </c>
+      <c r="I679" t="n">
+        <v>0</v>
+      </c>
+      <c r="J679" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B680" t="s">
+        <v>14</v>
+      </c>
+      <c r="C680" t="s">
+        <v>21</v>
+      </c>
+      <c r="D680" t="s">
+        <v>12</v>
+      </c>
+      <c r="E680" t="n">
+        <v>285</v>
+      </c>
+      <c r="F680" t="n">
+        <v>677</v>
+      </c>
+      <c r="G680" t="n">
+        <v>446</v>
+      </c>
+      <c r="H680" t="n">
+        <v>231</v>
+      </c>
+      <c r="I680" t="n">
+        <v>396</v>
+      </c>
+      <c r="J680" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B681" t="s">
+        <v>14</v>
+      </c>
+      <c r="C681" t="s">
+        <v>21</v>
+      </c>
+      <c r="D681" t="s">
+        <v>13</v>
+      </c>
+      <c r="E681" t="n">
+        <v>0</v>
+      </c>
+      <c r="F681" t="n">
+        <v>0</v>
+      </c>
+      <c r="G681" t="n">
+        <v>0</v>
+      </c>
+      <c r="H681" t="n">
+        <v>0</v>
+      </c>
+      <c r="I681" t="n">
+        <v>0</v>
+      </c>
+      <c r="J681" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B682" t="s">
+        <v>23</v>
+      </c>
+      <c r="C682" t="s">
+        <v>21</v>
+      </c>
+      <c r="D682" t="s">
+        <v>15</v>
+      </c>
+      <c r="E682" t="n">
+        <v>0</v>
+      </c>
+      <c r="F682" t="n">
+        <v>0</v>
+      </c>
+      <c r="G682" t="n">
+        <v>0</v>
+      </c>
+      <c r="H682" t="n">
+        <v>0</v>
+      </c>
+      <c r="I682" t="n">
+        <v>0</v>
+      </c>
+      <c r="J682" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B683" t="s">
+        <v>14</v>
+      </c>
+      <c r="C683" t="s">
+        <v>22</v>
+      </c>
+      <c r="D683" t="s">
+        <v>12</v>
+      </c>
+      <c r="E683" t="n">
+        <v>0</v>
+      </c>
+      <c r="F683" t="n">
+        <v>487</v>
+      </c>
+      <c r="G683" t="n">
+        <v>306</v>
+      </c>
+      <c r="H683" t="n">
+        <v>181</v>
+      </c>
+      <c r="I683" t="n">
+        <v>271</v>
+      </c>
+      <c r="J683" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B684" t="s">
+        <v>14</v>
+      </c>
+      <c r="C684" t="s">
+        <v>22</v>
+      </c>
+      <c r="D684" t="s">
+        <v>13</v>
+      </c>
+      <c r="E684" t="n">
+        <v>726</v>
+      </c>
+      <c r="F684" t="n">
+        <v>162</v>
+      </c>
+      <c r="G684" t="n">
+        <v>107</v>
+      </c>
+      <c r="H684" t="n">
+        <v>55</v>
+      </c>
+      <c r="I684" t="n">
+        <v>96</v>
+      </c>
+      <c r="J684" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B685" t="s">
+        <v>23</v>
+      </c>
+      <c r="C685" t="s">
+        <v>22</v>
+      </c>
+      <c r="D685" t="s">
+        <v>15</v>
+      </c>
+      <c r="E685" t="n">
+        <v>0</v>
+      </c>
+      <c r="F685" t="n">
+        <v>0</v>
+      </c>
+      <c r="G685" t="n">
+        <v>0</v>
+      </c>
+      <c r="H685" t="n">
+        <v>0</v>
+      </c>
+      <c r="I685" t="n">
+        <v>0</v>
+      </c>
+      <c r="J685" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B686" t="s">
+        <v>23</v>
+      </c>
+      <c r="C686" t="s">
+        <v>11</v>
+      </c>
+      <c r="D686" t="s">
+        <v>12</v>
+      </c>
+      <c r="E686" t="n">
+        <v>152</v>
+      </c>
+      <c r="F686" t="n">
+        <v>189</v>
+      </c>
+      <c r="G686" t="n">
+        <v>117</v>
+      </c>
+      <c r="H686" t="n">
+        <v>72</v>
+      </c>
+      <c r="I686" t="n">
+        <v>106</v>
+      </c>
+      <c r="J686" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B687" t="s">
+        <v>23</v>
+      </c>
+      <c r="C687" t="s">
+        <v>11</v>
+      </c>
+      <c r="D687" t="s">
+        <v>13</v>
+      </c>
+      <c r="E687" t="n">
+        <v>0</v>
+      </c>
+      <c r="F687" t="n">
+        <v>89</v>
+      </c>
+      <c r="G687" t="n">
+        <v>37</v>
+      </c>
+      <c r="H687" t="n">
+        <v>52</v>
+      </c>
+      <c r="I687" t="n">
+        <v>32</v>
+      </c>
+      <c r="J687" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B688" t="s">
+        <v>24</v>
+      </c>
+      <c r="C688" t="s">
+        <v>11</v>
+      </c>
+      <c r="D688" t="s">
+        <v>15</v>
+      </c>
+      <c r="E688" t="n">
+        <v>0</v>
+      </c>
+      <c r="F688" t="n">
+        <v>0</v>
+      </c>
+      <c r="G688" t="n">
+        <v>0</v>
+      </c>
+      <c r="H688" t="n">
+        <v>0</v>
+      </c>
+      <c r="I688" t="n">
+        <v>0</v>
+      </c>
+      <c r="J688" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B689" t="s">
+        <v>23</v>
+      </c>
+      <c r="C689" t="s">
+        <v>16</v>
+      </c>
+      <c r="D689" t="s">
+        <v>12</v>
+      </c>
+      <c r="E689" t="n">
+        <v>0</v>
+      </c>
+      <c r="F689" t="n">
+        <v>0</v>
+      </c>
+      <c r="G689" t="n">
+        <v>0</v>
+      </c>
+      <c r="H689" t="n">
+        <v>0</v>
+      </c>
+      <c r="I689" t="n">
+        <v>0</v>
+      </c>
+      <c r="J689" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B690" t="s">
+        <v>23</v>
+      </c>
+      <c r="C690" t="s">
+        <v>16</v>
+      </c>
+      <c r="D690" t="s">
+        <v>13</v>
+      </c>
+      <c r="E690" t="n">
+        <v>0</v>
+      </c>
+      <c r="F690" t="n">
+        <v>0</v>
+      </c>
+      <c r="G690" t="n">
+        <v>0</v>
+      </c>
+      <c r="H690" t="n">
+        <v>0</v>
+      </c>
+      <c r="I690" t="n">
+        <v>0</v>
+      </c>
+      <c r="J690" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B691" t="s">
+        <v>24</v>
+      </c>
+      <c r="C691" t="s">
+        <v>16</v>
+      </c>
+      <c r="D691" t="s">
+        <v>15</v>
+      </c>
+      <c r="E691" t="n">
+        <v>248</v>
+      </c>
+      <c r="F691" t="n">
+        <v>252</v>
+      </c>
+      <c r="G691" t="n">
+        <v>215</v>
+      </c>
+      <c r="H691" t="n">
+        <v>37</v>
+      </c>
+      <c r="I691" t="n">
+        <v>204</v>
+      </c>
+      <c r="J691" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B692" t="s">
+        <v>23</v>
+      </c>
+      <c r="C692" t="s">
+        <v>17</v>
+      </c>
+      <c r="D692" t="s">
+        <v>12</v>
+      </c>
+      <c r="E692" t="n">
+        <v>0</v>
+      </c>
+      <c r="F692" t="n">
+        <v>295</v>
+      </c>
+      <c r="G692" t="n">
+        <v>203</v>
+      </c>
+      <c r="H692" t="n">
+        <v>92</v>
+      </c>
+      <c r="I692" t="n">
+        <v>198</v>
+      </c>
+      <c r="J692" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B693" t="s">
+        <v>23</v>
+      </c>
+      <c r="C693" t="s">
+        <v>17</v>
+      </c>
+      <c r="D693" t="s">
+        <v>13</v>
+      </c>
+      <c r="E693" t="n">
+        <v>0</v>
+      </c>
+      <c r="F693" t="n">
+        <v>0</v>
+      </c>
+      <c r="G693" t="n">
+        <v>0</v>
+      </c>
+      <c r="H693" t="n">
+        <v>0</v>
+      </c>
+      <c r="I693" t="n">
+        <v>0</v>
+      </c>
+      <c r="J693" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B694" t="s">
+        <v>24</v>
+      </c>
+      <c r="C694" t="s">
+        <v>17</v>
+      </c>
+      <c r="D694" t="s">
+        <v>15</v>
+      </c>
+      <c r="E694" t="n">
+        <v>952</v>
+      </c>
+      <c r="F694" t="n">
+        <v>345</v>
+      </c>
+      <c r="G694" t="n">
+        <v>304</v>
+      </c>
+      <c r="H694" t="n">
+        <v>41</v>
+      </c>
+      <c r="I694" t="n">
+        <v>291</v>
+      </c>
+      <c r="J694" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B695" t="s">
+        <v>23</v>
+      </c>
+      <c r="C695" t="s">
+        <v>18</v>
+      </c>
+      <c r="D695" t="s">
+        <v>12</v>
+      </c>
+      <c r="E695" t="n">
+        <v>0</v>
+      </c>
+      <c r="F695" t="n">
+        <v>0</v>
+      </c>
+      <c r="G695" t="n">
+        <v>0</v>
+      </c>
+      <c r="H695" t="n">
+        <v>0</v>
+      </c>
+      <c r="I695" t="n">
+        <v>0</v>
+      </c>
+      <c r="J695" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B696" t="s">
+        <v>23</v>
+      </c>
+      <c r="C696" t="s">
+        <v>18</v>
+      </c>
+      <c r="D696" t="s">
+        <v>13</v>
+      </c>
+      <c r="E696" t="n">
+        <v>0</v>
+      </c>
+      <c r="F696" t="n">
+        <v>0</v>
+      </c>
+      <c r="G696" t="n">
+        <v>0</v>
+      </c>
+      <c r="H696" t="n">
+        <v>0</v>
+      </c>
+      <c r="I696" t="n">
+        <v>0</v>
+      </c>
+      <c r="J696" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B697" t="s">
+        <v>24</v>
+      </c>
+      <c r="C697" t="s">
+        <v>18</v>
+      </c>
+      <c r="D697" t="s">
+        <v>15</v>
+      </c>
+      <c r="E697" t="n">
+        <v>953</v>
+      </c>
+      <c r="F697" t="n">
+        <v>1161</v>
+      </c>
+      <c r="G697" t="n">
+        <v>1078</v>
+      </c>
+      <c r="H697" t="n">
+        <v>83</v>
+      </c>
+      <c r="I697" t="n">
+        <v>1059</v>
+      </c>
+      <c r="J697" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B698" t="s">
+        <v>23</v>
+      </c>
+      <c r="C698" t="s">
+        <v>19</v>
+      </c>
+      <c r="D698" t="s">
+        <v>12</v>
+      </c>
+      <c r="E698" t="n">
+        <v>347</v>
+      </c>
+      <c r="F698" t="n">
+        <v>322</v>
+      </c>
+      <c r="G698" t="n">
+        <v>169</v>
+      </c>
+      <c r="H698" t="n">
+        <v>153</v>
+      </c>
+      <c r="I698" t="n">
+        <v>144</v>
+      </c>
+      <c r="J698" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B699" t="s">
+        <v>23</v>
+      </c>
+      <c r="C699" t="s">
+        <v>19</v>
+      </c>
+      <c r="D699" t="s">
+        <v>13</v>
+      </c>
+      <c r="E699" t="n">
+        <v>0</v>
+      </c>
+      <c r="F699" t="n">
+        <v>0</v>
+      </c>
+      <c r="G699" t="n">
+        <v>0</v>
+      </c>
+      <c r="H699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I699" t="n">
+        <v>0</v>
+      </c>
+      <c r="J699" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B700" t="s">
+        <v>24</v>
+      </c>
+      <c r="C700" t="s">
+        <v>19</v>
+      </c>
+      <c r="D700" t="s">
+        <v>15</v>
+      </c>
+      <c r="E700" t="n">
+        <v>0</v>
+      </c>
+      <c r="F700" t="n">
+        <v>0</v>
+      </c>
+      <c r="G700" t="n">
+        <v>0</v>
+      </c>
+      <c r="H700" t="n">
+        <v>0</v>
+      </c>
+      <c r="I700" t="n">
+        <v>0</v>
+      </c>
+      <c r="J700" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B701" t="s">
+        <v>23</v>
+      </c>
+      <c r="C701" t="s">
+        <v>20</v>
+      </c>
+      <c r="D701" t="s">
+        <v>12</v>
+      </c>
+      <c r="E701" t="n">
+        <v>188</v>
+      </c>
+      <c r="F701" t="n">
+        <v>494</v>
+      </c>
+      <c r="G701" t="n">
+        <v>458</v>
+      </c>
+      <c r="H701" t="n">
+        <v>36</v>
+      </c>
+      <c r="I701" t="n">
+        <v>432</v>
+      </c>
+      <c r="J701" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B702" t="s">
+        <v>23</v>
+      </c>
+      <c r="C702" t="s">
+        <v>20</v>
+      </c>
+      <c r="D702" t="s">
+        <v>13</v>
+      </c>
+      <c r="E702" t="n">
+        <v>0</v>
+      </c>
+      <c r="F702" t="n">
+        <v>109</v>
+      </c>
+      <c r="G702" t="n">
+        <v>30</v>
+      </c>
+      <c r="H702" t="n">
+        <v>79</v>
+      </c>
+      <c r="I702" t="n">
+        <v>29</v>
+      </c>
+      <c r="J702" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B703" t="s">
+        <v>24</v>
+      </c>
+      <c r="C703" t="s">
+        <v>20</v>
+      </c>
+      <c r="D703" t="s">
+        <v>15</v>
+      </c>
+      <c r="E703" t="n">
+        <v>187</v>
+      </c>
+      <c r="F703" t="n">
+        <v>302</v>
+      </c>
+      <c r="G703" t="n">
+        <v>218</v>
+      </c>
+      <c r="H703" t="n">
+        <v>84</v>
+      </c>
+      <c r="I703" t="n">
+        <v>215</v>
+      </c>
+      <c r="J703" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B704" t="s">
+        <v>23</v>
+      </c>
+      <c r="C704" t="s">
+        <v>21</v>
+      </c>
+      <c r="D704" t="s">
+        <v>12</v>
+      </c>
+      <c r="E704" t="n">
+        <v>40</v>
+      </c>
+      <c r="F704" t="n">
+        <v>190</v>
+      </c>
+      <c r="G704" t="n">
+        <v>125</v>
+      </c>
+      <c r="H704" t="n">
+        <v>65</v>
+      </c>
+      <c r="I704" t="n">
+        <v>119</v>
+      </c>
+      <c r="J704" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B705" t="s">
+        <v>23</v>
+      </c>
+      <c r="C705" t="s">
+        <v>21</v>
+      </c>
+      <c r="D705" t="s">
+        <v>13</v>
+      </c>
+      <c r="E705" t="n">
+        <v>0</v>
+      </c>
+      <c r="F705" t="n">
+        <v>0</v>
+      </c>
+      <c r="G705" t="n">
+        <v>0</v>
+      </c>
+      <c r="H705" t="n">
+        <v>0</v>
+      </c>
+      <c r="I705" t="n">
+        <v>0</v>
+      </c>
+      <c r="J705" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B706" t="s">
+        <v>24</v>
+      </c>
+      <c r="C706" t="s">
+        <v>21</v>
+      </c>
+      <c r="D706" t="s">
+        <v>15</v>
+      </c>
+      <c r="E706" t="n">
+        <v>0</v>
+      </c>
+      <c r="F706" t="n">
+        <v>0</v>
+      </c>
+      <c r="G706" t="n">
+        <v>0</v>
+      </c>
+      <c r="H706" t="n">
+        <v>0</v>
+      </c>
+      <c r="I706" t="n">
+        <v>0</v>
+      </c>
+      <c r="J706" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B707" t="s">
+        <v>23</v>
+      </c>
+      <c r="C707" t="s">
+        <v>22</v>
+      </c>
+      <c r="D707" t="s">
+        <v>12</v>
+      </c>
+      <c r="E707" t="n">
+        <v>0</v>
+      </c>
+      <c r="F707" t="n">
+        <v>15</v>
+      </c>
+      <c r="G707" t="n">
+        <v>15</v>
+      </c>
+      <c r="H707" t="n">
+        <v>0</v>
+      </c>
+      <c r="I707" t="n">
+        <v>15</v>
+      </c>
+      <c r="J707" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B708" t="s">
+        <v>23</v>
+      </c>
+      <c r="C708" t="s">
+        <v>22</v>
+      </c>
+      <c r="D708" t="s">
+        <v>13</v>
+      </c>
+      <c r="E708" t="n">
+        <v>0</v>
+      </c>
+      <c r="F708" t="n">
+        <v>240</v>
+      </c>
+      <c r="G708" t="n">
+        <v>128</v>
+      </c>
+      <c r="H708" t="n">
+        <v>112</v>
+      </c>
+      <c r="I708" t="n">
+        <v>125</v>
+      </c>
+      <c r="J708" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B709" t="s">
+        <v>24</v>
+      </c>
+      <c r="C709" t="s">
+        <v>22</v>
+      </c>
+      <c r="D709" t="s">
+        <v>15</v>
+      </c>
+      <c r="E709" t="n">
+        <v>0</v>
+      </c>
+      <c r="F709" t="n">
+        <v>0</v>
+      </c>
+      <c r="G709" t="n">
+        <v>0</v>
+      </c>
+      <c r="H709" t="n">
+        <v>0</v>
+      </c>
+      <c r="I709" t="n">
+        <v>0</v>
+      </c>
+      <c r="J709" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B710" t="s">
+        <v>24</v>
+      </c>
+      <c r="C710" t="s">
+        <v>11</v>
+      </c>
+      <c r="D710" t="s">
+        <v>12</v>
+      </c>
+      <c r="E710" t="n">
+        <v>0</v>
+      </c>
+      <c r="F710" t="n">
+        <v>693</v>
+      </c>
+      <c r="G710" t="n">
+        <v>238</v>
+      </c>
+      <c r="H710" t="n">
+        <v>455</v>
+      </c>
+      <c r="I710" t="n">
+        <v>214</v>
+      </c>
+      <c r="J710" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B711" t="s">
+        <v>24</v>
+      </c>
+      <c r="C711" t="s">
+        <v>11</v>
+      </c>
+      <c r="D711" t="s">
+        <v>13</v>
+      </c>
+      <c r="E711" t="n">
+        <v>0</v>
+      </c>
+      <c r="F711" t="n">
+        <v>181</v>
+      </c>
+      <c r="G711" t="n">
+        <v>103</v>
+      </c>
+      <c r="H711" t="n">
+        <v>78</v>
+      </c>
+      <c r="I711" t="n">
+        <v>88</v>
+      </c>
+      <c r="J711" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B712" t="s">
+        <v>25</v>
+      </c>
+      <c r="C712" t="s">
+        <v>11</v>
+      </c>
+      <c r="D712" t="s">
+        <v>15</v>
+      </c>
+      <c r="E712" t="n">
+        <v>0</v>
+      </c>
+      <c r="F712" t="n">
+        <v>0</v>
+      </c>
+      <c r="G712" t="n">
+        <v>0</v>
+      </c>
+      <c r="H712" t="n">
+        <v>0</v>
+      </c>
+      <c r="I712" t="n">
+        <v>0</v>
+      </c>
+      <c r="J712" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B713" t="s">
+        <v>24</v>
+      </c>
+      <c r="C713" t="s">
+        <v>16</v>
+      </c>
+      <c r="D713" t="s">
+        <v>12</v>
+      </c>
+      <c r="E713" t="n">
+        <v>0</v>
+      </c>
+      <c r="F713" t="n">
+        <v>0</v>
+      </c>
+      <c r="G713" t="n">
+        <v>0</v>
+      </c>
+      <c r="H713" t="n">
+        <v>0</v>
+      </c>
+      <c r="I713" t="n">
+        <v>0</v>
+      </c>
+      <c r="J713" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B714" t="s">
+        <v>24</v>
+      </c>
+      <c r="C714" t="s">
+        <v>16</v>
+      </c>
+      <c r="D714" t="s">
+        <v>13</v>
+      </c>
+      <c r="E714" t="n">
+        <v>0</v>
+      </c>
+      <c r="F714" t="n">
+        <v>0</v>
+      </c>
+      <c r="G714" t="n">
+        <v>0</v>
+      </c>
+      <c r="H714" t="n">
+        <v>0</v>
+      </c>
+      <c r="I714" t="n">
+        <v>0</v>
+      </c>
+      <c r="J714" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B715" t="s">
+        <v>25</v>
+      </c>
+      <c r="C715" t="s">
+        <v>16</v>
+      </c>
+      <c r="D715" t="s">
+        <v>15</v>
+      </c>
+      <c r="E715" t="n">
+        <v>0</v>
+      </c>
+      <c r="F715" t="n">
+        <v>87</v>
+      </c>
+      <c r="G715" t="n">
+        <v>87</v>
+      </c>
+      <c r="H715" t="n">
+        <v>0</v>
+      </c>
+      <c r="I715" t="n">
+        <v>83</v>
+      </c>
+      <c r="J715" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B716" t="s">
+        <v>24</v>
+      </c>
+      <c r="C716" t="s">
+        <v>17</v>
+      </c>
+      <c r="D716" t="s">
+        <v>12</v>
+      </c>
+      <c r="E716" t="n">
+        <v>0</v>
+      </c>
+      <c r="F716" t="n">
+        <v>0</v>
+      </c>
+      <c r="G716" t="n">
+        <v>0</v>
+      </c>
+      <c r="H716" t="n">
+        <v>0</v>
+      </c>
+      <c r="I716" t="n">
+        <v>0</v>
+      </c>
+      <c r="J716" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B717" t="s">
+        <v>24</v>
+      </c>
+      <c r="C717" t="s">
+        <v>17</v>
+      </c>
+      <c r="D717" t="s">
+        <v>13</v>
+      </c>
+      <c r="E717" t="n">
+        <v>0</v>
+      </c>
+      <c r="F717" t="n">
+        <v>0</v>
+      </c>
+      <c r="G717" t="n">
+        <v>0</v>
+      </c>
+      <c r="H717" t="n">
+        <v>0</v>
+      </c>
+      <c r="I717" t="n">
+        <v>0</v>
+      </c>
+      <c r="J717" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B718" t="s">
+        <v>25</v>
+      </c>
+      <c r="C718" t="s">
+        <v>17</v>
+      </c>
+      <c r="D718" t="s">
+        <v>15</v>
+      </c>
+      <c r="E718" t="n">
+        <v>0</v>
+      </c>
+      <c r="F718" t="n">
+        <v>1114</v>
+      </c>
+      <c r="G718" t="n">
+        <v>860</v>
+      </c>
+      <c r="H718" t="n">
+        <v>254</v>
+      </c>
+      <c r="I718" t="n">
+        <v>843</v>
+      </c>
+      <c r="J718" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B719" t="s">
+        <v>24</v>
+      </c>
+      <c r="C719" t="s">
+        <v>18</v>
+      </c>
+      <c r="D719" t="s">
+        <v>12</v>
+      </c>
+      <c r="E719" t="n">
+        <v>0</v>
+      </c>
+      <c r="F719" t="n">
+        <v>0</v>
+      </c>
+      <c r="G719" t="n">
+        <v>0</v>
+      </c>
+      <c r="H719" t="n">
+        <v>0</v>
+      </c>
+      <c r="I719" t="n">
+        <v>0</v>
+      </c>
+      <c r="J719" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B720" t="s">
+        <v>24</v>
+      </c>
+      <c r="C720" t="s">
+        <v>18</v>
+      </c>
+      <c r="D720" t="s">
+        <v>13</v>
+      </c>
+      <c r="E720" t="n">
+        <v>0</v>
+      </c>
+      <c r="F720" t="n">
+        <v>0</v>
+      </c>
+      <c r="G720" t="n">
+        <v>0</v>
+      </c>
+      <c r="H720" t="n">
+        <v>0</v>
+      </c>
+      <c r="I720" t="n">
+        <v>0</v>
+      </c>
+      <c r="J720" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B721" t="s">
+        <v>25</v>
+      </c>
+      <c r="C721" t="s">
+        <v>18</v>
+      </c>
+      <c r="D721" t="s">
+        <v>15</v>
+      </c>
+      <c r="E721" t="n">
+        <v>0</v>
+      </c>
+      <c r="F721" t="n">
+        <v>755</v>
+      </c>
+      <c r="G721" t="n">
+        <v>701</v>
+      </c>
+      <c r="H721" t="n">
+        <v>54</v>
+      </c>
+      <c r="I721" t="n">
+        <v>689</v>
+      </c>
+      <c r="J721" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B722" t="s">
+        <v>24</v>
+      </c>
+      <c r="C722" t="s">
+        <v>19</v>
+      </c>
+      <c r="D722" t="s">
+        <v>12</v>
+      </c>
+      <c r="E722" t="n">
+        <v>0</v>
+      </c>
+      <c r="F722" t="n">
+        <v>695</v>
+      </c>
+      <c r="G722" t="n">
+        <v>422</v>
+      </c>
+      <c r="H722" t="n">
+        <v>273</v>
+      </c>
+      <c r="I722" t="n">
+        <v>370</v>
+      </c>
+      <c r="J722" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B723" t="s">
+        <v>24</v>
+      </c>
+      <c r="C723" t="s">
+        <v>19</v>
+      </c>
+      <c r="D723" t="s">
+        <v>13</v>
+      </c>
+      <c r="E723" t="n">
+        <v>0</v>
+      </c>
+      <c r="F723" t="n">
+        <v>6</v>
+      </c>
+      <c r="G723" t="n">
+        <v>6</v>
+      </c>
+      <c r="H723" t="n">
+        <v>0</v>
+      </c>
+      <c r="I723" t="n">
+        <v>4</v>
+      </c>
+      <c r="J723" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B724" t="s">
+        <v>25</v>
+      </c>
+      <c r="C724" t="s">
+        <v>19</v>
+      </c>
+      <c r="D724" t="s">
+        <v>15</v>
+      </c>
+      <c r="E724" t="n">
+        <v>0</v>
+      </c>
+      <c r="F724" t="n">
+        <v>99</v>
+      </c>
+      <c r="G724" t="n">
+        <v>65</v>
+      </c>
+      <c r="H724" t="n">
+        <v>34</v>
+      </c>
+      <c r="I724" t="n">
+        <v>58</v>
+      </c>
+      <c r="J724" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B725" t="s">
+        <v>24</v>
+      </c>
+      <c r="C725" t="s">
+        <v>20</v>
+      </c>
+      <c r="D725" t="s">
+        <v>12</v>
+      </c>
+      <c r="E725" t="n">
+        <v>0</v>
+      </c>
+      <c r="F725" t="n">
+        <v>112</v>
+      </c>
+      <c r="G725" t="n">
+        <v>34</v>
+      </c>
+      <c r="H725" t="n">
+        <v>78</v>
+      </c>
+      <c r="I725" t="n">
+        <v>32</v>
+      </c>
+      <c r="J725" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B726" t="s">
+        <v>24</v>
+      </c>
+      <c r="C726" t="s">
+        <v>20</v>
+      </c>
+      <c r="D726" t="s">
+        <v>13</v>
+      </c>
+      <c r="E726" t="n">
+        <v>0</v>
+      </c>
+      <c r="F726" t="n">
+        <v>136</v>
+      </c>
+      <c r="G726" t="n">
+        <v>48</v>
+      </c>
+      <c r="H726" t="n">
+        <v>88</v>
+      </c>
+      <c r="I726" t="n">
+        <v>39</v>
+      </c>
+      <c r="J726" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B727" t="s">
+        <v>25</v>
+      </c>
+      <c r="C727" t="s">
+        <v>20</v>
+      </c>
+      <c r="D727" t="s">
+        <v>15</v>
+      </c>
+      <c r="E727" t="n">
+        <v>0</v>
+      </c>
+      <c r="F727" t="n">
+        <v>309</v>
+      </c>
+      <c r="G727" t="n">
+        <v>217</v>
+      </c>
+      <c r="H727" t="n">
+        <v>92</v>
+      </c>
+      <c r="I727" t="n">
+        <v>214</v>
+      </c>
+      <c r="J727" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B728" t="s">
+        <v>24</v>
+      </c>
+      <c r="C728" t="s">
+        <v>21</v>
+      </c>
+      <c r="D728" t="s">
+        <v>12</v>
+      </c>
+      <c r="E728" t="n">
+        <v>0</v>
+      </c>
+      <c r="F728" t="n">
+        <v>500</v>
+      </c>
+      <c r="G728" t="n">
+        <v>218</v>
+      </c>
+      <c r="H728" t="n">
+        <v>282</v>
+      </c>
+      <c r="I728" t="n">
+        <v>173</v>
+      </c>
+      <c r="J728" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B729" t="s">
+        <v>24</v>
+      </c>
+      <c r="C729" t="s">
+        <v>21</v>
+      </c>
+      <c r="D729" t="s">
+        <v>13</v>
+      </c>
+      <c r="E729" t="n">
+        <v>0</v>
+      </c>
+      <c r="F729" t="n">
+        <v>121</v>
+      </c>
+      <c r="G729" t="n">
+        <v>46</v>
+      </c>
+      <c r="H729" t="n">
+        <v>75</v>
+      </c>
+      <c r="I729" t="n">
+        <v>41</v>
+      </c>
+      <c r="J729" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B730" t="s">
+        <v>25</v>
+      </c>
+      <c r="C730" t="s">
+        <v>21</v>
+      </c>
+      <c r="D730" t="s">
+        <v>15</v>
+      </c>
+      <c r="E730" t="n">
+        <v>0</v>
+      </c>
+      <c r="F730" t="n">
+        <v>0</v>
+      </c>
+      <c r="G730" t="n">
+        <v>0</v>
+      </c>
+      <c r="H730" t="n">
+        <v>0</v>
+      </c>
+      <c r="I730" t="n">
+        <v>0</v>
+      </c>
+      <c r="J730" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B731" t="s">
+        <v>24</v>
+      </c>
+      <c r="C731" t="s">
+        <v>22</v>
+      </c>
+      <c r="D731" t="s">
+        <v>12</v>
+      </c>
+      <c r="E731" t="n">
+        <v>0</v>
+      </c>
+      <c r="F731" t="n">
+        <v>351</v>
+      </c>
+      <c r="G731" t="n">
+        <v>118</v>
+      </c>
+      <c r="H731" t="n">
+        <v>233</v>
+      </c>
+      <c r="I731" t="n">
+        <v>108</v>
+      </c>
+      <c r="J731" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B732" t="s">
+        <v>24</v>
+      </c>
+      <c r="C732" t="s">
+        <v>22</v>
+      </c>
+      <c r="D732" t="s">
+        <v>13</v>
+      </c>
+      <c r="E732" t="n">
+        <v>0</v>
+      </c>
+      <c r="F732" t="n">
+        <v>319</v>
+      </c>
+      <c r="G732" t="n">
+        <v>163</v>
+      </c>
+      <c r="H732" t="n">
+        <v>156</v>
+      </c>
+      <c r="I732" t="n">
+        <v>150</v>
+      </c>
+      <c r="J732" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B733" t="s">
+        <v>25</v>
+      </c>
+      <c r="C733" t="s">
+        <v>22</v>
+      </c>
+      <c r="D733" t="s">
+        <v>15</v>
+      </c>
+      <c r="E733" t="n">
+        <v>0</v>
+      </c>
+      <c r="F733" t="n">
+        <v>0</v>
+      </c>
+      <c r="G733" t="n">
+        <v>0</v>
+      </c>
+      <c r="H733" t="n">
+        <v>0</v>
+      </c>
+      <c r="I733" t="n">
+        <v>0</v>
+      </c>
+      <c r="J733" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -18835,7 +23923,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -18877,7 +23965,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -18933,7 +24021,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -18975,7 +24063,7 @@
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
@@ -19045,7 +24133,7 @@
         <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
@@ -19101,7 +24189,7 @@
         <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
@@ -19199,7 +24287,7 @@
         <v>12</v>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
@@ -19213,7 +24301,7 @@
         <v>15</v>
       </c>
       <c r="C29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D29" t="s">
         <v>25</v>
@@ -19241,7 +24329,7 @@
         <v>12</v>
       </c>
       <c r="C31" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D31" t="s">
         <v>25</v>
@@ -19255,7 +24343,7 @@
         <v>15</v>
       </c>
       <c r="C32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32" t="s">
         <v>26</v>
@@ -19269,7 +24357,7 @@
         <v>13</v>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D33" t="s">
         <v>25</v>
@@ -19367,7 +24455,7 @@
         <v>12</v>
       </c>
       <c r="C40" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -19451,7 +24539,7 @@
         <v>15</v>
       </c>
       <c r="C46" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D46" t="s">
         <v>24</v>
@@ -19479,7 +24567,7 @@
         <v>12</v>
       </c>
       <c r="C48" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D48" t="s">
         <v>24</v>
@@ -19521,7 +24609,7 @@
         <v>12</v>
       </c>
       <c r="C51" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D51" t="s">
         <v>25</v>
@@ -19563,7 +24651,7 @@
         <v>12</v>
       </c>
       <c r="C54" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D54" t="s">
         <v>26</v>
@@ -19605,7 +24693,7 @@
         <v>12</v>
       </c>
       <c r="C57" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D57" t="s">
         <v>27</v>
@@ -19647,7 +24735,7 @@
         <v>12</v>
       </c>
       <c r="C60" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
@@ -19689,7 +24777,7 @@
         <v>12</v>
       </c>
       <c r="C63" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D63" t="s">
         <v>14</v>
@@ -19790,6 +24878,272 @@
         <v>11</v>
       </c>
       <c r="D70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" t="n">
+        <v>25</v>
+      </c>
+      <c r="D71" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B72" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" t="n">
+        <v>22</v>
+      </c>
+      <c r="D72" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B73" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" t="n">
+        <v>11</v>
+      </c>
+      <c r="D73" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" t="n">
+        <v>22</v>
+      </c>
+      <c r="D74" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B75" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75" t="n">
+        <v>22</v>
+      </c>
+      <c r="D75" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B76" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" t="n">
+        <v>25</v>
+      </c>
+      <c r="D76" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B77" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" t="n">
+        <v>22</v>
+      </c>
+      <c r="D77" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B78" t="s">
+        <v>13</v>
+      </c>
+      <c r="C78" t="n">
+        <v>13</v>
+      </c>
+      <c r="D78" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B79" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" t="n">
+        <v>23</v>
+      </c>
+      <c r="D79" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" t="n">
+        <v>21</v>
+      </c>
+      <c r="D80" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B81" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" t="n">
+        <v>11</v>
+      </c>
+      <c r="D81" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B82" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" t="n">
+        <v>25</v>
+      </c>
+      <c r="D82" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B83" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" t="n">
+        <v>7</v>
+      </c>
+      <c r="D83" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B84" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84" t="n">
+        <v>16</v>
+      </c>
+      <c r="D84" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B85" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" t="n">
+        <v>20</v>
+      </c>
+      <c r="D85" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B86" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" t="n">
+        <v>4</v>
+      </c>
+      <c r="D86" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87" t="n">
+        <v>24</v>
+      </c>
+      <c r="D87" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B88" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" t="n">
+        <v>22</v>
+      </c>
+      <c r="D88" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B89" t="s">
+        <v>13</v>
+      </c>
+      <c r="C89" t="n">
+        <v>9</v>
+      </c>
+      <c r="D89" t="s">
         <v>24</v>
       </c>
     </row>
